--- a/data/trans_orig/P43B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P43B-Estudios-trans_orig.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -525,25 +525,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha mamografía en 2012</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última mamografía en 2012 (tasa de respuesta: 98,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +547,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -563,17 +556,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -644,41 +626,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -701,13 +648,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -722,37 +662,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42678</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30779</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57608</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31200</t>
+          <t>30779</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57175</t>
+          <t>57608</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,47 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>42678</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>31200</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>57175</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -835,37 +740,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>740</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>789122</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>774192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>801021</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>774625</t>
+          <t>774192</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>800600</t>
+          <t>801021</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,47 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>789122</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>774625</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>800600</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>93,13%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>96,25%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -948,37 +818,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>779</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>831800</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>831800</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>831800</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1012,41 +882,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>779</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>831800</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>831800</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>831800</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1065,37 +900,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>121216</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101819</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>143779</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99546</t>
+          <t>101819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144128</t>
+          <t>143779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,47 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>121216</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>99546</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>144128</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>18,85%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>15,48%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>22,41%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -1178,37 +978,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>474</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>521962</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>499399</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>541359</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>499050</t>
+          <t>499399</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>543632</t>
+          <t>541359</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,47 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>521962</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>499050</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>543632</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>81,15%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>77,59%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>84,52%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -1291,37 +1056,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>643178</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>643178</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>643178</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1355,41 +1120,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>643178</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>643178</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>643178</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1408,37 +1138,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70141</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>85041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55312</t>
+          <t>56878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>85041</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,47 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>70141</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>55312</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>83780</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>44,26%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>34,9%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>52,87%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -1521,37 +1216,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88327</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73427</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101590</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74688</t>
+          <t>73427</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103156</t>
+          <t>101590</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,47 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>88327</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>74688</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>103156</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>55,74%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>47,13%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>65,1%</t>
+          <t>64,11%</t>
         </is>
       </c>
     </row>
@@ -1634,37 +1294,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>133</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158468</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158468</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158468</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1698,41 +1358,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>158468</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>158468</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>158468</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1751,37 +1376,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234035</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>206545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>265551</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>206323</t>
+          <t>206545</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>264876</t>
+          <t>265551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,47 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>234035</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>206323</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>264876</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>14,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -1864,37 +1454,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1399412</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1367896</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1426902</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1368571</t>
+          <t>1367896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1427124</t>
+          <t>1426902</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,47 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1399412</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1368571</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1427124</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>85,67%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>87,37%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>
@@ -1977,37 +1532,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1633447</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1633447</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1633447</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2041,41 +1596,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1492</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1633447</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1633447</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1633447</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2089,13 +1609,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2109,7 +1628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2128,25 +1647,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha mamografía en 2016</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última mamografía en 2016 (tasa de respuesta: 96,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +1669,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2166,17 +1678,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2247,41 +1748,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2304,13 +1770,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2325,37 +1784,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17049</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +1829,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>17049</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37328</t>
+          <t>37062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,47 +1844,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>25556</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>16819</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>37328</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -2438,37 +1862,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>520</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>582288</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>570782</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>590795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +1907,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>570516</t>
+          <t>570782</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>591025</t>
+          <t>590795</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,47 +1922,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>582288</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>570516</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>591025</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -2551,37 +1940,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>544</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>607844</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>607844</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>607844</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2615,41 +2004,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>607844</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>607844</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>607844</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2668,37 +2022,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>82901</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>65578</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102420</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2067,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64938</t>
+          <t>65578</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103316</t>
+          <t>102420</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,47 +2082,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>82901</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>64938</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>103316</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -2781,37 +2100,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>687</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>750751</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>731232</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>768074</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2145,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>730336</t>
+          <t>731232</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>768714</t>
+          <t>768074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,47 +2160,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>750751</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>730336</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>768714</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>90,06%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>87,61%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>92,21%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -2894,37 +2178,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>762</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>833652</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>833652</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>833652</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2958,41 +2242,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>833652</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>833652</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>833652</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3011,37 +2260,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97512</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>82476</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115554</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +2305,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81624</t>
+          <t>82476</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113677</t>
+          <t>115554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,47 +2320,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>97512</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>81624</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>113677</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>40,29%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>33,72%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>46,96%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -3124,37 +2338,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>144539</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159575</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +2383,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128374</t>
+          <t>126497</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160427</t>
+          <t>159575</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,47 +2398,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>144539</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>128374</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>160427</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>59,71%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>53,04%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>66,28%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -3237,37 +2416,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>222</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>242051</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>242051</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>242051</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3301,41 +2480,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>242051</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>242051</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>242051</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3354,37 +2498,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>187</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>205969</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>179551</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237812</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +2543,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>179593</t>
+          <t>179551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>237257</t>
+          <t>237812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,42 +2563,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>205969</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>179593</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>237257</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>12,23%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>14,09%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -3467,37 +2576,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1477578</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1445735</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1503996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +2621,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1446290</t>
+          <t>1445735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1503954</t>
+          <t>1503996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,45 +2636,10 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>89,33%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1341</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1477578</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1446290</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1503954</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>87,77%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>85,91%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>89,33%</t>
         </is>
@@ -3580,37 +2654,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1683547</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1683547</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1683547</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3644,41 +2718,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1528</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1683547</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1683547</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1683547</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3692,13 +2731,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -3712,7 +2750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3731,25 +2769,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha mamografía en 2023</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última mamografía en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +2791,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3769,17 +2800,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3850,41 +2870,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3907,13 +2892,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3928,37 +2906,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +2951,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28522</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,47 +2966,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>19055</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>13005</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>28522</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -4041,37 +2984,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>760</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>378570</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>368999</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>384693</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +3029,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>369103</t>
+          <t>368999</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>384620</t>
+          <t>384693</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,47 +3044,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>378570</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>369103</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>384620</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>95,21%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>92,83%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -4154,37 +3062,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>792</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>397625</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>397625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>397625</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4218,41 +3126,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>397625</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>397625</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>397625</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4271,37 +3144,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>171</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104093</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>52125</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>142642</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +3189,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54121</t>
+          <t>52125</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139973</t>
+          <t>142642</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,47 +3204,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>104093</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>54121</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>139973</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>15,33%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -4384,37 +3222,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>809190</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>770641</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>861158</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +3267,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>773310</t>
+          <t>770641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>859162</t>
+          <t>861158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,47 +3282,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1025</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>809190</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>773310</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>859162</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>88,6%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>84,67%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>94,07%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -4497,37 +3300,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>913283</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>913283</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>913283</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4561,41 +3364,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1196</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>913283</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>913283</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>913283</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4614,37 +3382,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>199</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>121637</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>108619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135084</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +3427,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108921</t>
+          <t>108619</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135072</t>
+          <t>135084</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,47 +3442,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>121637</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>108921</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>135072</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>45,4%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>40,65%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>50,41%</t>
+          <t>50,42%</t>
         </is>
       </c>
     </row>
@@ -4727,37 +3460,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>272</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>146296</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>132849</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +3505,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132861</t>
+          <t>132849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159012</t>
+          <t>159314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,47 +3520,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>146296</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>132861</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>159012</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>54,6%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>49,59%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>59,35%</t>
+          <t>59,46%</t>
         </is>
       </c>
     </row>
@@ -4840,37 +3538,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267933</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267933</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267933</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4904,41 +3602,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>267933</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>267933</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>267933</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4957,37 +3620,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>402</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>244786</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156220</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>292978</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +3665,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>150721</t>
+          <t>156220</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>293109</t>
+          <t>292978</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,45 +3680,10 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>18,56%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>244786</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>150721</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>293109</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>18,56%</t>
         </is>
@@ -5070,37 +3698,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1334056</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1285864</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +3743,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1285733</t>
+          <t>1285864</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1428121</t>
+          <t>1422622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5135,42 +3763,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2057</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1334056</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1285733</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1428121</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>84,5%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>81,44%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>90,45%</t>
+          <t>90,11%</t>
         </is>
       </c>
     </row>
@@ -5183,37 +3776,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1578842</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1578842</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1578842</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5247,41 +3840,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>2459</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1578842</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1578842</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1578842</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5295,13 +3853,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P43B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P43B-Estudios-trans_orig.xlsx
@@ -672,12 +672,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30779</t>
+          <t>31988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57608</t>
+          <t>57022</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30779</t>
+          <t>31988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57608</t>
+          <t>57022</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>774192</t>
+          <t>774778</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>801021</t>
+          <t>799812</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>774192</t>
+          <t>774778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>801021</t>
+          <t>799812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101819</t>
+          <t>96810</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143779</t>
+          <t>141822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>101819</t>
+          <t>96810</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>143779</t>
+          <t>141822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>499399</t>
+          <t>501356</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>541359</t>
+          <t>546368</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>499399</t>
+          <t>501356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>541359</t>
+          <t>546368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,95%</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56878</t>
+          <t>57245</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85041</t>
+          <t>84634</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56878</t>
+          <t>57245</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85041</t>
+          <t>84634</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73427</t>
+          <t>73834</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101590</t>
+          <t>101223</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73427</t>
+          <t>73834</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101590</t>
+          <t>101223</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,88%</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>206545</t>
+          <t>206651</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>265551</t>
+          <t>264318</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>206545</t>
+          <t>206651</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>265551</t>
+          <t>264318</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1367896</t>
+          <t>1369129</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1426902</t>
+          <t>1426796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1367896</t>
+          <t>1369129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1426902</t>
+          <t>1426796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17049</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37062</t>
+          <t>37760</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17049</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37062</t>
+          <t>37760</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>570782</t>
+          <t>570084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>590795</t>
+          <t>590586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>570782</t>
+          <t>570084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>590795</t>
+          <t>590586</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65578</t>
+          <t>63678</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102420</t>
+          <t>99792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65578</t>
+          <t>63678</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102420</t>
+          <t>99792</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>731232</t>
+          <t>733860</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>768074</t>
+          <t>769974</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>731232</t>
+          <t>733860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>768074</t>
+          <t>769974</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82476</t>
+          <t>81518</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115554</t>
+          <t>112255</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82476</t>
+          <t>81518</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115554</t>
+          <t>112255</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>46,38%</t>
         </is>
       </c>
     </row>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>126497</t>
+          <t>129796</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>159575</t>
+          <t>160533</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126497</t>
+          <t>129796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159575</t>
+          <t>160533</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,32%</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>179551</t>
+          <t>177688</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>237812</t>
+          <t>234490</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>179551</t>
+          <t>177688</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>237812</t>
+          <t>234490</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1445735</t>
+          <t>1449057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1503996</t>
+          <t>1505859</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1445735</t>
+          <t>1449057</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1503996</t>
+          <t>1505859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -2911,32 +2911,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>20200</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12932</t>
+          <t>14428</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>29654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>20200</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12932</t>
+          <t>14428</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>29654</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>378570</t>
+          <t>410786</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>368999</t>
+          <t>401332</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384693</t>
+          <t>416558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>378570</t>
+          <t>410786</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>368999</t>
+          <t>401332</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>384693</t>
+          <t>416558</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -3067,17 +3067,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>397625</t>
+          <t>430986</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>397625</t>
+          <t>430986</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>397625</t>
+          <t>430986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3102,17 +3102,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>397625</t>
+          <t>430986</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>397625</t>
+          <t>430986</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>397625</t>
+          <t>430986</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>104093</t>
+          <t>115173</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52125</t>
+          <t>100676</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>142642</t>
+          <t>131870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>104093</t>
+          <t>115173</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52125</t>
+          <t>100676</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>142642</t>
+          <t>131870</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>809190</t>
+          <t>616666</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>770641</t>
+          <t>599969</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>861158</t>
+          <t>631163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>809190</t>
+          <t>616666</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>770641</t>
+          <t>599969</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>861158</t>
+          <t>631163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -3305,17 +3305,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>913283</t>
+          <t>731839</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>913283</t>
+          <t>731839</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>913283</t>
+          <t>731839</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>913283</t>
+          <t>731839</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>913283</t>
+          <t>731839</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>913283</t>
+          <t>731839</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3387,32 +3387,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>121637</t>
+          <t>133590</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108619</t>
+          <t>119584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135084</t>
+          <t>147325</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3422,32 +3422,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>121637</t>
+          <t>133590</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108619</t>
+          <t>119584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135084</t>
+          <t>147325</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>49,25%</t>
         </is>
       </c>
     </row>
@@ -3465,32 +3465,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>146296</t>
+          <t>165517</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>132849</t>
+          <t>151782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>159314</t>
+          <t>179523</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3500,32 +3500,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>146296</t>
+          <t>165517</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132849</t>
+          <t>151782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159314</t>
+          <t>179523</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>60,02%</t>
         </is>
       </c>
     </row>
@@ -3543,17 +3543,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>267933</t>
+          <t>299107</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>267933</t>
+          <t>299107</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>267933</t>
+          <t>299107</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3578,17 +3578,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>267933</t>
+          <t>299107</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>267933</t>
+          <t>299107</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>267933</t>
+          <t>299107</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3625,32 +3625,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>244786</t>
+          <t>268963</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>156220</t>
+          <t>244931</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>292978</t>
+          <t>294912</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3660,32 +3660,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>244786</t>
+          <t>268963</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156220</t>
+          <t>244931</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>292978</t>
+          <t>294912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -3703,32 +3703,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1334056</t>
+          <t>1192969</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1285864</t>
+          <t>1167020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1422622</t>
+          <t>1217001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3738,32 +3738,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1334056</t>
+          <t>1192969</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1285864</t>
+          <t>1167020</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1422622</t>
+          <t>1217001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -3781,17 +3781,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1578842</t>
+          <t>1461932</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1578842</t>
+          <t>1461932</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1578842</t>
+          <t>1461932</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3816,17 +3816,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1578842</t>
+          <t>1461932</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1578842</t>
+          <t>1461932</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1578842</t>
+          <t>1461932</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
